--- a/datos.xlsx
+++ b/datos.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Leeme" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="88">
   <si>
     <t>Hoja de captura — Pipeline Calidad y Atención (V2)</t>
   </si>
@@ -286,6 +286,12 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prueba dos </t>
+  </si>
+  <si>
+    <t>prueba dos</t>
   </si>
 </sst>
 </file>
@@ -413,7 +419,6 @@
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -455,6 +460,7 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -727,55 +733,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
     </row>
@@ -796,175 +802,175 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>0</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>1</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>1</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>1</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>2</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>2</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>2</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>2</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="7">
-        <v>3</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="B10" s="6">
+        <v>3</v>
+      </c>
+      <c r="C10" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="7">
-        <v>3</v>
-      </c>
-      <c r="C11" s="7">
+      <c r="B11" s="6">
+        <v>3</v>
+      </c>
+      <c r="C11" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1"/>
@@ -987,263 +993,277 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="10">
         <v>46256</v>
       </c>
-      <c r="E2" s="10">
-        <v>3</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="E2" s="9">
+        <v>3</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="9">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>46261</v>
       </c>
-      <c r="E3" s="10">
-        <v>3</v>
-      </c>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="9">
+        <v>3</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="10">
         <v>46268</v>
       </c>
-      <c r="E4" s="10">
-        <v>3</v>
-      </c>
-      <c r="F4" s="10" t="s">
+      <c r="E4" s="9">
+        <v>3</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11">
         <v>46275</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <v>2</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
+      <c r="A6" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="11">
+        <v>46285</v>
+      </c>
+      <c r="E6" s="7">
+        <v>3</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="7">
+        <v>7</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1"/>
@@ -1285,517 +1305,531 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="13">
+      <c r="D2" s="12">
         <v>4</v>
       </c>
-      <c r="E2" s="13">
-        <v>3</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="E2" s="12">
+        <v>3</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="12">
         <v>6</v>
       </c>
-      <c r="E3" s="13">
-        <v>3</v>
-      </c>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="12">
+        <v>3</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="12">
         <v>1.2</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="13">
-        <v>3</v>
-      </c>
-      <c r="E4" s="13">
-        <v>3</v>
-      </c>
-      <c r="F4" s="10" t="s">
+      <c r="D4" s="12">
+        <v>3</v>
+      </c>
+      <c r="E4" s="12">
+        <v>3</v>
+      </c>
+      <c r="F4" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="13">
-        <v>3</v>
-      </c>
-      <c r="E5" s="13">
-        <v>3</v>
-      </c>
-      <c r="F5" s="10" t="s">
+      <c r="D5" s="12">
+        <v>3</v>
+      </c>
+      <c r="E5" s="12">
+        <v>3</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="12">
         <v>4</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="12">
         <v>5</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="12">
         <v>1.5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="13">
-        <v>3</v>
-      </c>
-      <c r="E7" s="13">
-        <v>3</v>
-      </c>
-      <c r="F7" s="10" t="s">
+      <c r="D7" s="12">
+        <v>3</v>
+      </c>
+      <c r="E7" s="12">
+        <v>3</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <v>4</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <v>5</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <v>1.5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="8">
-        <v>3</v>
-      </c>
-      <c r="E9" s="8">
-        <v>3</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="D9" s="7">
+        <v>3</v>
+      </c>
+      <c r="E9" s="7">
+        <v>3</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="A10" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="7">
+        <v>6</v>
+      </c>
+      <c r="E10" s="7">
+        <v>6</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1"/>
@@ -1827,181 +1861,181 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="14" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>2</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B5" s="7">
-        <v>3</v>
-      </c>
-      <c r="D5" s="17" t="s">
+      <c r="B5" s="6">
+        <v>3</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>5</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="7">
-        <v>3</v>
-      </c>
-      <c r="D7" s="17" t="s">
+      <c r="B7" s="6">
+        <v>3</v>
+      </c>
+      <c r="D7" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>2</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>4</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>9</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="1"/>
+      <c r="E11" s="17"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="6">
         <v>1</v>
       </c>
     </row>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -24,39 +24,39 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="85">
-  <si>
-    <t xml:space="preserve">Hoja de captura — Pipeline Calidad y Atención (V3)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="85">
+  <si>
+    <t xml:space="preserve">Hoja de captura — Pipeline Calidad y Atención</t>
   </si>
   <si>
     <t xml:space="preserve">Localidades</t>
   </si>
   <si>
-    <t xml:space="preserve">Ciudad → días de ida → días de retorno. La localidad del evento mueve transporte de ida y retorno.</t>
+    <t xml:space="preserve">Ciudad → días de ida → días de retorno (ida = vuelta). La localidad del evento mueve transporte de ida y retorno.</t>
   </si>
   <si>
     <t xml:space="preserve">Eventos</t>
   </si>
   <si>
-    <t xml:space="preserve">Un renglón por evento: localidad (combo), fecha, días, y material de largo plazo con su lead (vidrio, acrílico…).</t>
+    <t xml:space="preserve">Un renglón por evento: localidad (menú), fecha, días de evento, y DÍAS DE MONTAJE y DESMONTAJE (los define el recinto/comité, por eso van aquí).</t>
   </si>
   <si>
     <t xml:space="preserve">Elementos</t>
   </si>
   <si>
-    <t xml:space="preserve">Un renglón por elemento (Stand, Escenografía, Módulo, Arco). DÍAS FABRICACIÓN = estimación del experto (un número). ESTADO = para el tablero Kanban. Dos pisos = Sí dispara la escalera (7 días háb.). Ancho×Largo informativo.</t>
+    <t xml:space="preserve">Un renglón por elemento. EVENTO se elige de un menú. DÍAS FABRICACIÓN = estimación del experto. ESTADO = Kanban. Dos pisos = Sí dispara la escalera. MATERIALES (verde): Vidrio/Acrílico/Lona Sí/No — pueden ser VARIOS por elemento.</t>
   </si>
   <si>
     <t xml:space="preserve">Parametros</t>
   </si>
   <si>
-    <t xml:space="preserve">Fases del proceso + % carpintería (resto pintura) + día extra de presión a carpintería + capacidad + calendario (sáb ½, dom no).</t>
+    <t xml:space="preserve">Fases de oficina/compra + carga + transporte/retorno base local + acomodo + capacidad + % carpintería + leads + calendario (sáb ½, dom no).</t>
   </si>
   <si>
     <t xml:space="preserve">Cómo se usa</t>
   </si>
   <si>
-    <t xml:space="preserve">La app web carga este Excel y muestra DOS vistas: GANTT (cuándo) y KANBAN (en qué estado va). Impresión: en paralelo a pintura, no se captura.</t>
+    <t xml:space="preserve">La app carga este Excel y muestra Gantt · Kanban · Pendientes. Los materiales se amarran a la carga − colchón; 'Por pedir' muestra su fecha límite con semáforo.</t>
   </si>
   <si>
     <t xml:space="preserve">Ciudad</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">Días evento</t>
   </si>
   <si>
-    <t xml:space="preserve">Material largo plazo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead material (días háb.)</t>
+    <t xml:space="preserve">Días montaje</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días desmontaje</t>
   </si>
   <si>
     <t xml:space="preserve">Anestesiología (Conexxión)</t>
@@ -125,40 +125,40 @@
     <t xml:space="preserve">WTC</t>
   </si>
   <si>
-    <t xml:space="preserve">Ninguno</t>
-  </si>
-  <si>
     <t xml:space="preserve">Glaucoma</t>
   </si>
   <si>
+    <t xml:space="preserve">Expo Fire (FM Approvals)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elemento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancho (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Largo (m)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dos pisos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días fabricación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vidrio templado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Acrílico</t>
   </si>
   <si>
-    <t xml:space="preserve">Expo Fire (FM Approvals)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vidrio templado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elemento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ancho (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Largo (m)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dos pisos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Días fabricación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estado</t>
+    <t xml:space="preserve">Lona/impresión especial</t>
   </si>
   <si>
     <t xml:space="preserve">Stand principal</t>
@@ -179,6 +179,9 @@
     <t xml:space="preserve">Pintura</t>
   </si>
   <si>
+    <t xml:space="preserve">Sí</t>
+  </si>
+  <si>
     <t xml:space="preserve">Isla B</t>
   </si>
   <si>
@@ -191,9 +194,6 @@
     <t xml:space="preserve">Doble altura</t>
   </si>
   <si>
-    <t xml:space="preserve">Sí</t>
-  </si>
-  <si>
     <t xml:space="preserve">Registro</t>
   </si>
   <si>
@@ -251,34 +251,34 @@
     <t xml:space="preserve">Compra de materiales</t>
   </si>
   <si>
+    <t xml:space="preserve">Lead vidrio templado (días háb.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carga de camión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead acrílico (días háb.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transporte (base local)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead lona/impresión especial (días háb.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retorno (base local)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sábado (fracción de turno)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pre-armado y verificación</t>
+    <t xml:space="preserve">Acomodo en bodega</t>
   </si>
   <si>
     <t xml:space="preserve">Domingo (fracción)</t>
   </si>
   <si>
-    <t xml:space="preserve">Carga de camión</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación: el experto captura DÍAS por elemento. La app reparte % carpintería / resto pintura y suma el día extra a carpintería.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transporte (base local)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaje en sitio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desmontaje</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retorno (base local)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acomodo en bodega</t>
+    <t xml:space="preserve">Montaje y desmontaje ahora se capturan POR EVENTO (los define el recinto/comité).</t>
   </si>
 </sst>
 </file>
@@ -383,7 +383,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -400,6 +400,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF3B0"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCFCE7"/>
+        <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -452,7 +458,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -473,36 +479,28 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -516,6 +514,10 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -555,7 +557,7 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFDCFCE7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF1D4ED8"/>
@@ -781,7 +783,7 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="110"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="120"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -975,52 +977,52 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7"/>
+      <c r="A12" s="5"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7"/>
+      <c r="A13" s="5"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7"/>
+      <c r="A14" s="5"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
+      <c r="A15" s="5"/>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
+      <c r="A16" s="5"/>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
+      <c r="A17" s="5"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
+      <c r="A18" s="5"/>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7"/>
+      <c r="A19" s="5"/>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
+      <c r="A20" s="5"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7"/>
+      <c r="A21" s="5"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
     </row>
@@ -1049,10 +1051,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>24</v>
       </c>
@@ -1076,236 +1079,232 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="8" t="n">
         <v>46256</v>
       </c>
-      <c r="E2" s="9" t="n">
+      <c r="E2" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G2" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="B3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="10" t="n">
-        <v>46261</v>
-      </c>
-      <c r="E3" s="9" t="n">
+      <c r="B4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>46268</v>
+      </c>
+      <c r="E4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="9" t="n">
+      <c r="F4" s="7" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>46268</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>7</v>
+      <c r="G4" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="11"/>
+      <c r="D5" s="8"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="11"/>
+      <c r="D6" s="8"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="11"/>
+      <c r="D7" s="8"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="11"/>
+      <c r="D8" s="8"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="11"/>
+      <c r="D9" s="8"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="11"/>
+      <c r="D10" s="8"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="11"/>
+      <c r="D11" s="8"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="11"/>
+      <c r="D12" s="8"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="11"/>
+      <c r="D13" s="8"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="11"/>
+      <c r="D14" s="8"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="11"/>
+      <c r="D15" s="8"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="11"/>
+      <c r="D16" s="8"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
       <c r="C17" s="7"/>
-      <c r="D17" s="11"/>
+      <c r="D17" s="8"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="11"/>
+      <c r="D18" s="8"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="11"/>
+      <c r="D19" s="8"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
       <c r="C20" s="7"/>
-      <c r="D20" s="11"/>
+      <c r="D20" s="8"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="11"/>
+      <c r="D21" s="8"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true"/>
-  <dataValidations count="2">
+  <dataValidations count="1">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C21" type="list">
       <formula1>Localidades!$A$2:$A$21</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F2:F21" type="list">
-      <formula1>"Ninguno,Acrílico,Vidrio templado,Lona/impresión especial,Otro"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -1324,577 +1323,761 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="12" t="n">
+      <c r="D2" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E2" s="12" t="n">
+      <c r="E2" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="12" t="n">
+      <c r="G2" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="7" t="s">
         <v>48</v>
       </c>
+      <c r="I2" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E3" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="C8" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" s="8" t="s">
+      <c r="G8" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="9" t="s">
+      <c r="J8" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>58</v>
+      <c r="K8" s="10" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
       <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="G9" s="9"/>
       <c r="H9" s="7"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
       <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
+      <c r="G10" s="9"/>
       <c r="H10" s="7"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
       <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
+      <c r="G11" s="9"/>
       <c r="H11" s="7"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
       <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="G12" s="9"/>
       <c r="H12" s="7"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
       <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
+      <c r="G13" s="9"/>
       <c r="H13" s="7"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
       <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
       <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+      <c r="G14" s="9"/>
       <c r="H14" s="7"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
       <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
+      <c r="G15" s="9"/>
       <c r="H15" s="7"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
       <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="G16" s="9"/>
       <c r="H16" s="7"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
       <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
+      <c r="G17" s="9"/>
       <c r="H17" s="7"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
       <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="G18" s="9"/>
       <c r="H18" s="7"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
       <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
       <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+      <c r="G19" s="9"/>
       <c r="H19" s="7"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
       <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
       <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
+      <c r="G20" s="9"/>
       <c r="H20" s="7"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
       <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
+      <c r="G21" s="9"/>
       <c r="H21" s="7"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
       <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
       <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
+      <c r="G22" s="9"/>
       <c r="H22" s="7"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
       <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
+      <c r="G23" s="9"/>
       <c r="H23" s="7"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
       <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
       <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+      <c r="G24" s="9"/>
       <c r="H24" s="7"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
       <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
+      <c r="G25" s="9"/>
       <c r="H25" s="7"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
       <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
       <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
+      <c r="G26" s="9"/>
       <c r="H26" s="7"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
       <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
       <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
+      <c r="G27" s="9"/>
       <c r="H27" s="7"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
       <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
       <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
+      <c r="G28" s="9"/>
       <c r="H28" s="7"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
       <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
+      <c r="G29" s="9"/>
       <c r="H29" s="7"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
       <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
       <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
+      <c r="G30" s="9"/>
       <c r="H30" s="7"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7"/>
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
       <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
       <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
+      <c r="G31" s="9"/>
       <c r="H31" s="7"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
       <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
       <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
+      <c r="G32" s="9"/>
       <c r="H32" s="7"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
+      <c r="A33" s="5"/>
+      <c r="B33" s="5"/>
       <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
       <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
+      <c r="G33" s="9"/>
       <c r="H33" s="7"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
+      <c r="G34" s="9"/>
       <c r="H34" s="7"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
+      <c r="A35" s="5"/>
+      <c r="B35" s="5"/>
       <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
       <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
+      <c r="G35" s="9"/>
       <c r="H35" s="7"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
+      <c r="A36" s="5"/>
+      <c r="B36" s="5"/>
       <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
       <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
+      <c r="G36" s="9"/>
       <c r="H36" s="7"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7"/>
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
       <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
+      <c r="G37" s="9"/>
       <c r="H37" s="7"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
       <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
       <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
+      <c r="G38" s="9"/>
       <c r="H38" s="7"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
       <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
+      <c r="G39" s="9"/>
       <c r="H39" s="7"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
       <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
       <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
+      <c r="G40" s="9"/>
       <c r="H40" s="7"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="7"/>
-      <c r="B41" s="7"/>
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
       <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
+      <c r="G41" s="9"/>
       <c r="H41" s="7"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7"/>
-      <c r="B42" s="7"/>
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
       <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
+      <c r="G42" s="9"/>
       <c r="H42" s="7"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
       <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
+      <c r="G43" s="9"/>
       <c r="H43" s="7"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true"/>
-  <dataValidations count="3">
+  <dataValidations count="7">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="A2:A44" type="list">
+      <formula1>Eventos!$A$2:$A$21</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C44" type="list">
       <formula1>"Stand,Escenografía,Módulo de registro,Arco"</formula1>
       <formula2>0</formula2>
@@ -1905,6 +2088,18 @@
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H44" type="list">
       <formula1>"Propuesta,Planos,Fabricación,Pintura,En montaje,Evento,Cerrado"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I44" type="list">
+      <formula1>"Sí,No"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J44" type="list">
+      <formula1>"Sí,No"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K2:K44" type="list">
+      <formula1>"Sí,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -1923,193 +2118,189 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="14" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="14" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="14" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E8" s="14" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E9" s="14" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="14" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="E10" s="6" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="14" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" s="17"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
+      <c r="D16" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="6" t="n">
-        <v>1</v>
-      </c>
+      <c r="E16" s="16"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true"/>
   <mergeCells count="1">
-    <mergeCell ref="D11:E13"/>
+    <mergeCell ref="D16:E17"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="84">
   <si>
     <t xml:space="preserve">Hoja de captura — Pipeline Calidad y Atención</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">Eventos</t>
   </si>
   <si>
-    <t xml:space="preserve">Un renglón por evento: localidad (menú), fecha, días de evento, y DÍAS DE MONTAJE y DESMONTAJE (los define el recinto/comité, por eso van aquí).</t>
+    <t xml:space="preserve">Un renglón por evento: localidad (menú), fecha, días de evento, DÍAS DE MONTAJE y DESMONTAJE (los define el recinto/comité). PLANOS BAJADOS = marca Sí cuando el diseñador ya entregó los planos a producción (déjalo vacío/No si aún no bajan; la app usará el Estado mientras tanto).</t>
   </si>
   <si>
     <t xml:space="preserve">Elementos</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Parametros</t>
   </si>
   <si>
-    <t xml:space="preserve">Fases de oficina/compra + carga + transporte/retorno base local + acomodo + capacidad + % carpintería + leads + calendario (sáb ½, dom no).</t>
+    <t xml:space="preserve">Fases de oficina + carga + transporte/retorno base local + acomodo + capacidad + % carpintería + leads + calendario (sáb ½, dom no).</t>
   </si>
   <si>
     <t xml:space="preserve">Cómo se usa</t>
@@ -119,6 +119,9 @@
     <t xml:space="preserve">Días desmontaje</t>
   </si>
   <si>
+    <t xml:space="preserve">Planos bajados</t>
+  </si>
+  <si>
     <t xml:space="preserve">Anestesiología (Conexxión)</t>
   </si>
   <si>
@@ -242,37 +245,31 @@
     <t xml:space="preserve">Lead escalera (días hábiles)</t>
   </si>
   <si>
-    <t xml:space="preserve">Planeación de producción</t>
+    <t xml:space="preserve">Carga de camión</t>
   </si>
   <si>
     <t xml:space="preserve">Colchón material antes de carga (días háb.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Compra de materiales</t>
+    <t xml:space="preserve">Transporte (base local)</t>
   </si>
   <si>
     <t xml:space="preserve">Lead vidrio templado (días háb.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Carga de camión</t>
+    <t xml:space="preserve">Retorno (base local)</t>
   </si>
   <si>
     <t xml:space="preserve">Lead acrílico (días háb.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Transporte (base local)</t>
+    <t xml:space="preserve">Acomodo en bodega</t>
   </si>
   <si>
     <t xml:space="preserve">Lead lona/impresión especial (días háb.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Retorno (base local)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sábado (fracción de turno)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acomodo en bodega</t>
   </si>
   <si>
     <t xml:space="preserve">Domingo (fracción)</t>
@@ -1043,7 +1040,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -1052,7 +1049,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1077,13 +1074,16 @@
       <c r="G1" s="4" t="s">
         <v>30</v>
       </c>
+      <c r="H1" s="4" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>14</v>
@@ -1100,13 +1100,14 @@
       <c r="G2" s="7" t="n">
         <v>1</v>
       </c>
+      <c r="H2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>32</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>14</v>
@@ -1123,10 +1124,11 @@
       <c r="G3" s="7" t="n">
         <v>1</v>
       </c>
+      <c r="H3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>15</v>
@@ -1146,6 +1148,7 @@
       <c r="G4" s="7" t="n">
         <v>1</v>
       </c>
+      <c r="H4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
@@ -1155,6 +1158,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -1164,6 +1168,7 @@
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -1173,6 +1178,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -1182,6 +1188,7 @@
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -1191,6 +1198,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -1200,6 +1208,7 @@
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
@@ -1209,6 +1218,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
@@ -1218,6 +1228,7 @@
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
@@ -1227,6 +1238,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
@@ -1236,6 +1248,7 @@
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
@@ -1245,6 +1258,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
@@ -1254,6 +1268,7 @@
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
@@ -1263,6 +1278,7 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
@@ -1272,6 +1288,7 @@
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
@@ -1281,6 +1298,7 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
@@ -1290,6 +1308,7 @@
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
@@ -1299,12 +1318,17 @@
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C21" type="list">
       <formula1>Localidades!$A$2:$A$21</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H21" type="list">
+      <formula1>"Sí,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -1341,45 +1365,45 @@
         <v>24</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D2" s="9" t="n">
         <v>4</v>
@@ -1388,33 +1412,33 @@
         <v>3</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G2" s="9" t="n">
         <v>6</v>
       </c>
       <c r="H2" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="10" t="s">
-        <v>47</v>
-      </c>
       <c r="J2" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" s="9" t="n">
         <v>6</v>
@@ -1423,33 +1447,33 @@
         <v>3</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G3" s="9" t="n">
         <v>8</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J3" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" s="9" t="n">
         <v>3</v>
@@ -1458,33 +1482,33 @@
         <v>3</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>3</v>
@@ -1493,33 +1517,33 @@
         <v>3</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="10" t="s">
-        <v>47</v>
-      </c>
       <c r="J5" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>4</v>
@@ -1528,33 +1552,33 @@
         <v>5</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" s="9" t="n">
         <v>12</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>3</v>
@@ -1563,33 +1587,33 @@
         <v>3</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>4</v>
@@ -1598,22 +1622,22 @@
         <v>5</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>10</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2130,32 +2154,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4" s="14" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E4" s="14" t="n">
         <v>3</v>
@@ -2163,13 +2187,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="14" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E5" s="14" t="n">
         <v>0.4</v>
@@ -2177,13 +2201,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B6" s="14" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E6" s="14" t="n">
         <v>1</v>
@@ -2191,13 +2215,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="14" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E7" s="14" t="n">
         <v>7</v>
@@ -2205,13 +2229,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B8" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>3</v>
@@ -2219,13 +2243,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B9" s="14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>7</v>
@@ -2233,13 +2257,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B10" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>3</v>
@@ -2247,25 +2271,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B11" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="14" t="n">
-        <v>1</v>
-      </c>
       <c r="D12" s="15" t="s">
         <v>81</v>
       </c>
@@ -2274,14 +2292,8 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
+      <c r="D13" s="15" t="s">
         <v>82</v>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>83</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>0</v>
@@ -2289,7 +2301,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D16" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E16" s="16"/>
     </row>

--- a/datos.xlsx
+++ b/datos.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="83">
   <si>
     <t xml:space="preserve">Hoja de captura — Pipeline Calidad y Atención</t>
   </si>
@@ -173,13 +173,10 @@
     <t xml:space="preserve">No</t>
   </si>
   <si>
-    <t xml:space="preserve">Fabricación</t>
+    <t xml:space="preserve">Producción</t>
   </si>
   <si>
     <t xml:space="preserve">Isla A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pintura</t>
   </si>
   <si>
     <t xml:space="preserve">Sí</t>
@@ -1453,10 +1450,10 @@
         <v>8</v>
       </c>
       <c r="H3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I3" s="10" t="s">
         <v>51</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>52</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>48</v>
@@ -1470,7 +1467,7 @@
         <v>34</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>47</v>
@@ -1488,7 +1485,7 @@
         <v>4</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I4" s="10" t="s">
         <v>48</v>
@@ -1505,7 +1502,7 @@
         <v>34</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>47</v>
@@ -1540,7 +1537,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>47</v>
@@ -1552,19 +1549,19 @@
         <v>5</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6" s="9" t="n">
         <v>12</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I6" s="10" t="s">
         <v>48</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K6" s="10" t="s">
         <v>48</v>
@@ -1575,10 +1572,10 @@
         <v>34</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>3</v>
@@ -1593,7 +1590,7 @@
         <v>3</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>48</v>
@@ -1628,16 +1625,16 @@
         <v>10</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>48</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2111,7 +2108,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H44" type="list">
-      <formula1>"Propuesta,Planos,Fabricación,Pintura,En montaje,Evento,Cerrado"</formula1>
+      <formula1>"Propuesta,Planos,Producción,En montaje,Evento,Cerrado"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I44" type="list">
@@ -2154,32 +2151,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>63</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="14" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" s="14" t="n">
         <v>3</v>
@@ -2187,13 +2184,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5" s="14" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" s="14" t="n">
         <v>0.4</v>
@@ -2201,13 +2198,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6" s="14" t="n">
         <v>5</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E6" s="14" t="n">
         <v>1</v>
@@ -2215,13 +2212,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B7" s="14" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E7" s="14" t="n">
         <v>7</v>
@@ -2229,13 +2226,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B8" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E8" s="14" t="n">
         <v>3</v>
@@ -2243,13 +2240,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E9" s="14" t="n">
         <v>7</v>
@@ -2257,13 +2254,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E10" s="14" t="n">
         <v>3</v>
@@ -2271,13 +2268,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B11" s="14" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="14" t="n">
         <v>4</v>
@@ -2285,7 +2282,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E12" s="14" t="n">
         <v>0.5</v>
@@ -2293,7 +2290,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E13" s="14" t="n">
         <v>0</v>
@@ -2301,7 +2298,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D16" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E16" s="16"/>
     </row>
